--- a/results/2_controlli_oracle/controlli_f1.xlsx
+++ b/results/2_controlli_oracle/controlli_f1.xlsx
@@ -10313,7 +10313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -10322,75 +10322,82 @@
     <row r="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>Controlli SOLO ANALISI (voci 162-169): F1 per esercizio, 54 esercizi di validazione, 1 ripetizione (Gemma 4 26B A4B QAT).</t>
+          <t>Controlli SOLO ANALISI (voci 162-171): F1 per esercizio, 54 esercizi di validazione, 1 ripetizione (Gemma 4 26B A4B QAT).</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Difficoltà: Flesch-Kincaid Grade Level della traccia (textstat 0.7.4; più alto = più difficile) e grandezza = classi + relazioni del GT, generalizzazioni comprese. Un foglio per ciascun ordinamento (decrescente: il più difficile in alto); la colonna usata per ordinare ha l'intestazione rossa. Primo foglio: la GRANDEZZA, difficoltà dominante (Spearman con la completezza circa −0,45 contro circa −0,2 di Flesch-Kincaid sui 54); a parità di valore decide l'altra difficoltà, poi il nome dell'esercizio.</t>
+          <t xml:space="preserve">  ESCLUSI DALL'ANALISI STATISTICA (voce 172): l'analisi statistica riguarda solo il passo 3b; questi controlli vanno negli sviluppi futuri della tesi, come descrizione.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  F1 = media degli F1 di classi, attributi, relazioni e generalizzazioni (evaluation/element_metrics.py, abbinamento rilassato; tipologie assenti sia nel GT sia nella risposta escluse). Metrica NOSTRA: lo strumento dei relatori non ha valutato queste run.</t>
+          <t xml:space="preserve">  Difficoltà: Flesch-Kincaid Grade Level della traccia (textstat 0.7.4; più alto = più difficile) e grandezza = classi + relazioni del GT, generalizzazioni comprese. Un foglio per ciascun ordinamento (decrescente: il più difficile in alto); la colonna usata per ordinare ha l'intestazione rossa. Primo foglio: la GRANDEZZA, difficoltà dominante (Spearman con la completezza circa −0,45 contro circa −0,2 di Flesch-Kincaid sui 54); a parità di valore decide l'altra difficoltà, poi il nome dell'esercizio.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Colonne '3b ... (riferimento)': media delle 3 ripetizioni del passo 3b, per confronto.</t>
+          <t xml:space="preserve">  F1 = media degli F1 di classi, attributi, relazioni e generalizzazioni (evaluation/element_metrics.py, abbinamento rilassato; tipologie assenti sia nel GT sia nella risposta escluse). Metrica NOSTRA: lo strumento dei relatori non ha valutato queste run.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  esercizio stesso = il diagramma di riferimento dell'esercizio come unico esempio (voce 162; blocco standard = testo degli esempi del 3b, libero = 'mostra il formato e lo stile').</t>
+          <t xml:space="preserve">  Colonne '3b ... (riferimento)': media delle 3 ripetizioni del passo 3b, per confronto.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  parziale X % = solo X % delle classi dell'esercizio stesso, con le relazioni tra quelle classi (voce 163).</t>
+          <t xml:space="preserve">  esercizio stesso = il diagramma di riferimento dell'esercizio come unico esempio (voce 162; blocco standard = testo degli esempi del 3b, libero = 'mostra il formato e lo stile').</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  meta' + 2 bm25 = meta' dell'esercizio stesso + i 2 esempi bm25 k2; due meta' = le due meta' complementari come due esempi (voci 164-165); nel compatto dalla voce 170.</t>
+          <t xml:space="preserve">  parziale X % = solo X % delle classi dell'esercizio stesso, con le relazioni tra quelle classi (voce 163).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  senza attributi = esempi con classi e relazioni ma attributi tolti (valori degli enum e metodi restano): esercizio stesso, oppure gli esempi bm25 k3 del 3b (voci 167 e 169).</t>
+          <t xml:space="preserve">  meta' + 2 bm25 = meta' dell'esercizio stesso + i 2 esempi bm25 k2; due meta' = le due meta' complementari come due esempi (voci 164-165); nel compatto dalla voce 170.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Risposte non valide escluse: PlantUML / 3b zero_shot (riferimento): 1; JSON compatto / 3b zero_shot (riferimento): 2; JSON compatto / 3b bm25 k3 (riferimento): 1.</t>
+          <t xml:space="preserve">  senza attributi = esempi con classi e relazioni ma attributi tolti (valori degli enum e metodi restano): esercizio stesso, oppure gli esempi bm25 k3 del 3b (voci 167 e 169).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tutte le run dei controlli presenti.</t>
+          <t xml:space="preserve">  Risposte non valide escluse: PlantUML / 3b zero_shot (riferimento): 1; JSON compatto / 3b zero_shot (riferimento): 2; JSON compatto / 3b bm25 k3 (riferimento): 1.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tutte le run dei controlli presenti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  Generato da experiments/build_results.py.</t>
         </is>
